--- a/Test_Cases/05_Player/Notes_Player_Test_Cases.xlsx
+++ b/Test_Cases/05_Player/Notes_Player_Test_Cases.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,20 +432,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="78" customWidth="1" min="9" max="9"/>
-    <col width="78" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="84" customWidth="1" min="8" max="8"/>
+    <col width="82" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,8 +859,118 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-NOT-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Verify Notes player does not expose an editing UI</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Editing scope</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Scope / Regression</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Notes Player is open.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Notes.
+2. Inspect available controls.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>No editing UI is present in the documented code path; editing is not treated as a supported capability.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Notes remains open.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC-NOT-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Verify closing Notes restores prior board view when it is the last player</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Last player close</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Known board pan/zoom before Notes opens.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Known pan/zoom</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1. Set board pan/zoom.
+2. Open Notes.
+3. Close Notes.
+4. Observe board.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Prior board position and zoom are restored.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Whiteboard is returned to prior view.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K7"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -871,17 +981,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1058,8 +1168,52 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC-NOT-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Verify Notes player does not expose an editing UI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC-NOT-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Verify closing Notes restores prior board view when it is the last player</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>